--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20232.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20232.xlsx
@@ -67,49 +67,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
     <t>AQUINO</t>
   </si>
   <si>
-    <t>CASANOVA</t>
+    <t>BERTELY</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>GALINDO</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -118,58 +124,52 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>ILIAN ANELI</t>
+  </si>
+  <si>
     <t>JURISEL</t>
   </si>
   <si>
-    <t>LUCIA</t>
+    <t>MIGUEL</t>
   </si>
   <si>
     <t>DANIEL DE JESUS</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
     <t>MICHEL LEONEL</t>
   </si>
   <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
   </si>
   <si>
     <t>AARON</t>
@@ -641,16 +641,19 @@
         <v>23</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>23</v>
       </c>
-      <c r="E2">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -754,7 +757,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920281</v>
+        <v>23330051920308</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -777,7 +780,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920347</v>
+        <v>23330051920322</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -795,12 +798,12 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920285</v>
+        <v>23330051920281</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -818,12 +821,12 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920299</v>
+        <v>23330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -841,12 +844,12 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920348</v>
+        <v>23330051920285</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -864,12 +867,12 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920322</v>
+        <v>23330051920292</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -892,7 +895,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920284</v>
+        <v>23330051920295</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -915,13 +918,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920292</v>
+        <v>23330051920296</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -938,13 +941,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920295</v>
+        <v>23330051920299</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
@@ -961,13 +964,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920296</v>
+        <v>23330051920301</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>49</v>
@@ -984,13 +987,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920301</v>
+        <v>23330051920348</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>

--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20232.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -67,34 +67,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
+    <t>PELAYO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -106,28 +112,34 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -139,34 +151,40 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ILIAN ANELI</t>
+  </si>
+  <si>
+    <t>JURISEL</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>JUSTIN GIOVANNI</t>
   </si>
   <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
+    <t>IVAN JESUS</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -725,7 +743,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -757,16 +775,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920308</v>
+        <v>23330051920320</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -786,10 +804,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -809,10 +827,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -832,10 +850,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -855,10 +873,10 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -878,10 +896,10 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -901,10 +919,10 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -924,10 +942,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -947,10 +965,10 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -973,7 +991,7 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -987,16 +1005,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920348</v>
+        <v>23330051920308</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1010,16 +1028,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920363</v>
+        <v>23330051920309</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1033,16 +1051,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920326</v>
+        <v>23330051920348</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1051,6 +1069,52 @@
         <v>9</v>
       </c>
       <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920363</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920326</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20232.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,135 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELAYO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>IVAN JESUS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>YURI MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -724,16 +595,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.3</v>
+      </c>
+      <c r="H2">
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -773,351 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920320</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920281</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920284</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920285</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920292</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920295</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920296</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920299</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920301</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920308</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920348</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920363</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920326</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
